--- a/Swinburne/COS30045/data/usstates/info/info.xlsx
+++ b/Swinburne/COS30045/data/usstates/info/info.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\An\Documents\GitHub\Courseworks\Swinburne\COS30045\data\usstates\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4945625A-5AB8-4761-BB9B-E4E0159FC88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B2A6A3-3FBE-461A-816D-98AE9F15A172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="24" r:id="rId1"/>
     <sheet name="calc" sheetId="27" r:id="rId2"/>
-    <sheet name="groups" sheetId="28" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="_2014_eGRID_Subregion_File">#REF!</definedName>
@@ -4679,13 +4678,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B029DEF0-D257-4915-9371-77A06085F9C2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>